--- a/ContratosYReembolsos/Data/SeedData/FuneralServices.xlsx
+++ b/ContratosYReembolsos/Data/SeedData/FuneralServices.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\desarrollo\Documents\SeedData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AF75F871-4F50-4173-8A71-CB5595C1508A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEFC750E-B339-4C0C-ABD4-0035635F593A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FA51A0F0-52BA-4549-AE29-9B3C6DA60EB1}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="74">
   <si>
     <t>Id</t>
   </si>
@@ -51,9 +51,6 @@
     <t>Description</t>
   </si>
   <si>
-    <t>IsActive</t>
-  </si>
-  <si>
     <t>Ataúd</t>
   </si>
   <si>
@@ -256,6 +253,12 @@
   </si>
   <si>
     <t>Espacio reducido en muro destinado exclusivamente a guardar urnas con cenizas.</t>
+  </si>
+  <si>
+    <t>IsActiveInternal</t>
+  </si>
+  <si>
+    <t>IsActiveExternal</t>
   </si>
 </sst>
 </file>
@@ -291,8 +294,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -311,14 +315,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4E628CC1-85D8-438E-AB2E-9C07971F14AB}" name="Tabla11" displayName="Tabla11" ref="A1:E35" totalsRowShown="0">
-  <autoFilter ref="A1:E35" xr:uid="{E56CAAAA-E9D9-4A29-B93F-5332B48EAC07}"/>
-  <tableColumns count="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4E628CC1-85D8-438E-AB2E-9C07971F14AB}" name="Tabla11" displayName="Tabla11" ref="A1:F35" totalsRowShown="0">
+  <autoFilter ref="A1:F35" xr:uid="{E56CAAAA-E9D9-4A29-B93F-5332B48EAC07}"/>
+  <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{B727090F-CC28-4C39-95BD-9E7A171F4819}" name="Id"/>
     <tableColumn id="2" xr3:uid="{C56E108B-B33F-469A-9766-CB3D5382463E}" name="Name"/>
     <tableColumn id="3" xr3:uid="{38714165-B749-44CE-9F2E-08A4B18D26F1}" name="Price"/>
     <tableColumn id="4" xr3:uid="{777EB4BC-F8A7-4D16-B44E-3F14B9A6BEDB}" name="Description"/>
-    <tableColumn id="5" xr3:uid="{5546D51E-4A21-4E77-85B2-F68A79EF5A95}" name="IsActive"/>
+    <tableColumn id="5" xr3:uid="{5546D51E-4A21-4E77-85B2-F68A79EF5A95}" name="IsActiveInternal"/>
+    <tableColumn id="6" xr3:uid="{DF14C181-6856-4858-99F9-8A427F0A3BA0}" name="IsActiveExternal"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -621,14 +626,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0E2EABC-64CB-4DD0-822A-34CFF8C119C8}">
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="30.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="79.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -642,589 +647,695 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
         <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
       </c>
       <c r="C2">
         <v>2500</v>
       </c>
       <c r="D2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C3">
         <v>600</v>
       </c>
       <c r="D3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F3" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C4">
         <v>8500</v>
       </c>
       <c r="D4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F4" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C5">
         <v>1200</v>
       </c>
       <c r="D5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F5" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C6">
         <v>15000</v>
       </c>
       <c r="D6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F6" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C7">
         <v>1500</v>
       </c>
       <c r="D7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E7">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F7" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C8">
         <v>800</v>
       </c>
       <c r="D8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E8">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F8" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C9">
         <v>350</v>
       </c>
       <c r="D9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E9">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F9" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C10">
         <v>1200</v>
       </c>
       <c r="D10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E10">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F10" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C11">
         <v>3500</v>
       </c>
       <c r="D11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E11">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F11" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C12">
         <v>2000</v>
       </c>
       <c r="D12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E12">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F12" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C13">
         <v>500</v>
       </c>
       <c r="D13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E13">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F13" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C14">
         <v>700</v>
       </c>
       <c r="D14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E14">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F14" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C15">
         <v>300</v>
       </c>
       <c r="D15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E15">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F15" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C16">
         <v>600</v>
       </c>
       <c r="D16" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E16">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F16" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C17">
         <v>2800</v>
       </c>
       <c r="D17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E17">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F17" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C18">
         <v>250</v>
       </c>
       <c r="D18" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E18">
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F18" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C19">
         <v>450</v>
       </c>
       <c r="D19" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E19">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F19" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C20">
         <v>500</v>
       </c>
       <c r="D20" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E20">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F20" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C21">
         <v>1500</v>
       </c>
       <c r="D21" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E21">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F21" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C22">
         <v>2000</v>
       </c>
       <c r="D22" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E22">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F22" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C23">
         <v>900</v>
       </c>
       <c r="D23" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E23">
         <v>1</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F23" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C24">
         <v>3500</v>
       </c>
       <c r="D24" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E24">
         <v>1</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F24" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C25">
         <v>450</v>
       </c>
       <c r="D25" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E25">
         <v>1</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F25" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C26">
         <v>200</v>
       </c>
       <c r="D26" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E26">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F26" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C27">
         <v>4000</v>
       </c>
       <c r="D27" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E27">
         <v>1</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F27" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C28">
         <v>25000</v>
       </c>
       <c r="D28" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E28">
         <v>1</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F28" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C29">
         <v>250</v>
       </c>
       <c r="D29" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E29">
         <v>1</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F29" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C30">
         <v>600</v>
       </c>
       <c r="D30" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E30">
         <v>1</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F30" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C31">
         <v>18000</v>
       </c>
       <c r="D31" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E31">
         <v>1</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F31" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C32">
         <v>800</v>
       </c>
       <c r="D32" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E32">
         <v>1</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F32" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C33">
         <v>65000</v>
       </c>
       <c r="D33" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E33">
         <v>1</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F33" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C34">
         <v>1800</v>
       </c>
       <c r="D34" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E34">
         <v>1</v>
       </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F34" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C35">
         <v>2500</v>
       </c>
       <c r="D35" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E35">
+        <v>1</v>
+      </c>
+      <c r="F35" s="1">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
